--- a/peta-kerawanan/dist/template_sistem_500kv_jamali.xlsx
+++ b/peta-kerawanan/dist/template_sistem_500kv_jamali.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,6 +91,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,17 +473,17 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Nama Asset / GI</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Kode Singkatan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Tipe Simbol SLD</t>
         </is>
@@ -485,12 +498,12 @@
           <t>Kapasitas (MVA / MW)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Tier (Mulai 0)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Tegangan</t>
         </is>
@@ -500,12 +513,12 @@
           <t>No IBT</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
@@ -4037,12 +4050,12 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Nama Penghantar</t>
         </is>
@@ -4057,7 +4070,7 @@
           <t>Tipe Simbol SLD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Dari GI</t>
         </is>
@@ -4067,12 +4080,12 @@
           <t>Tipe Simbol Dari GI</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Tier Dari GI</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Ke GI</t>
         </is>
@@ -4082,12 +4095,12 @@
           <t>Tipe Simbol Ke GI</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Tier Ke GI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Tegangan</t>
         </is>
@@ -4107,7 +4120,7 @@
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Tingkat Kerawanan</t>
         </is>
@@ -8761,12 +8774,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
@@ -8781,7 +8794,7 @@
           <t>UIT</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Kondisi / Permasalahan</t>
         </is>
